--- a/nriss-patch-1/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:58:08+00:00</t>
+    <t>2026-06-01T14:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,11 +263,11 @@
     <t>Date de la saisie.</t>
   </si>
   <si>
-    <t>fr-lm-operateur-saisie.operateurSaisie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-operateur-saisie.operateurSaisie[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient</t>
   </si>
   <si>
     <t>Opérateur de saisie</t>
@@ -575,8 +575,8 @@
   <dimension ref="A1:AJ4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="30.84765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.84765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.00390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.00390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -585,7 +585,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -606,7 +606,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="30.84765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="33.00390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/nriss-patch-1/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-lm-operateur-saisie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
